--- a/diseases/d003/2000-2004.xlsx
+++ b/diseases/d003/2000-2004.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2552,6 +2612,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO14" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2700,6 +2765,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO15" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2848,6 +2918,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO16" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2996,6 +3071,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO17" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3537,6 +3617,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO20" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3685,6 +3770,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO21" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3833,6 +3923,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO22" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -3981,6 +4076,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO23" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4129,6 +4229,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO24" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4277,6 +4382,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO25" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4425,6 +4535,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO26" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4573,6 +4688,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO27" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4721,6 +4841,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO28" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -4869,6 +4994,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO29" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5017,6 +5147,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO30" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -5163,6 +5298,11 @@
       <c r="S31" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO31" t="inlineStr">

--- a/diseases/d003/2000-2004.xlsx
+++ b/diseases/d003/2000-2004.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.004412259560257887</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,22 +783,12 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>8.893545931847882</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,22 +921,12 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0.06177163384361041</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,22 +1059,12 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>14.27341224144111</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,22 +1197,12 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0.8692151333708037</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,22 +1335,12 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>2.186937524224889</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,22 +1473,12 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>1.050117775341377</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,22 +1611,12 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0.2332733359173215</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,22 +1749,12 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0.06177163384361041</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,22 +1887,12 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,22 +2025,12 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,22 +2163,12 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,22 +2301,12 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2760,11 +2565,6 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2777,22 +2577,12 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2913,11 +2703,6 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2930,22 +2715,12 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3066,11 +2841,6 @@
       <c r="R17" t="n">
         <v>0.004412259560257887</v>
       </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3083,22 +2853,12 @@
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr"/>
       <c r="AT17" t="n">
         <v>0</v>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV17" t="inlineStr">
         <is>
@@ -3612,11 +3372,6 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3629,22 +3384,12 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3765,11 +3510,6 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3782,22 +3522,12 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3918,11 +3648,6 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3935,22 +3660,12 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -4071,11 +3786,6 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4088,22 +3798,12 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -4224,11 +3924,6 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
-      <c r="S24" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4241,22 +3936,12 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR24" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
-      </c>
-      <c r="AU24" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4377,11 +4062,6 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4394,22 +4074,12 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR25" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
-      </c>
-      <c r="AU25" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4530,11 +4200,6 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
-      <c r="S26" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4547,22 +4212,12 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR26" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
-      </c>
-      <c r="AU26" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4683,11 +4338,6 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4700,22 +4350,12 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR27" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
-      </c>
-      <c r="AU27" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4836,11 +4476,6 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
-      <c r="S28" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4853,22 +4488,12 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR28" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
-      </c>
-      <c r="AU28" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4989,11 +4614,6 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
-      <c r="S29" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5006,22 +4626,12 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR29" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
-      </c>
-      <c r="AU29" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -5142,11 +4752,6 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
-      <c r="S30" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5159,22 +4764,12 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR30" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
-      </c>
-      <c r="AU30" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -5295,11 +4890,6 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
-      <c r="S31" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -5312,22 +4902,12 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR31" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
-      </c>
-      <c r="AU31" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>

--- a/diseases/d003/2000-2004.xlsx
+++ b/diseases/d003/2000-2004.xlsx
@@ -909,6 +909,11 @@
       <c r="R3" t="n">
         <v>8.893545931847882</v>
       </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -921,12 +926,22 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
@@ -1185,6 +1200,11 @@
       <c r="R5" t="n">
         <v>14.27341224144111</v>
       </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1197,12 +1217,22 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
@@ -1461,6 +1491,11 @@
       <c r="R7" t="n">
         <v>2.186937524224889</v>
       </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1473,12 +1508,22 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
@@ -1737,6 +1782,11 @@
       <c r="R9" t="n">
         <v>0.2332733359173215</v>
       </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1749,12 +1799,22 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
@@ -2013,6 +2073,11 @@
       <c r="R11" t="n">
         <v>0</v>
       </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2025,12 +2090,22 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
@@ -2151,6 +2226,11 @@
       <c r="R12" t="n">
         <v>0</v>
       </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2163,12 +2243,22 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
@@ -2289,6 +2379,11 @@
       <c r="R13" t="n">
         <v>0</v>
       </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2301,12 +2396,22 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
@@ -2427,6 +2532,11 @@
       <c r="R14" t="n">
         <v>0</v>
       </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2439,12 +2549,22 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
@@ -2565,6 +2685,11 @@
       <c r="R15" t="n">
         <v>0</v>
       </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2577,12 +2702,22 @@
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr"/>
       <c r="AT15" t="n">
         <v>0</v>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV15" t="inlineStr">
         <is>
@@ -2703,6 +2838,11 @@
       <c r="R16" t="n">
         <v>0</v>
       </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2715,12 +2855,22 @@
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr"/>
       <c r="AT16" t="n">
         <v>0</v>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV16" t="inlineStr">
         <is>
@@ -3372,6 +3522,11 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3384,12 +3539,22 @@
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr"/>
       <c r="AT20" t="n">
         <v>0</v>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV20" t="inlineStr">
         <is>
@@ -3510,6 +3675,11 @@
       <c r="R21" t="n">
         <v>0</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3522,12 +3692,22 @@
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr"/>
       <c r="AT21" t="n">
         <v>0</v>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV21" t="inlineStr">
         <is>
@@ -3648,6 +3828,11 @@
       <c r="R22" t="n">
         <v>0</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3660,12 +3845,22 @@
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr"/>
       <c r="AT22" t="n">
         <v>0</v>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV22" t="inlineStr">
         <is>
@@ -3786,6 +3981,11 @@
       <c r="R23" t="n">
         <v>0</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3798,12 +3998,22 @@
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr"/>
       <c r="AT23" t="n">
         <v>0</v>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV23" t="inlineStr">
         <is>
@@ -3924,6 +4134,11 @@
       <c r="R24" t="n">
         <v>0</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -3936,12 +4151,22 @@
       </c>
       <c r="AP24" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR24" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS24" t="inlineStr"/>
       <c r="AT24" t="n">
         <v>0</v>
+      </c>
+      <c r="AU24" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV24" t="inlineStr">
         <is>
@@ -4062,6 +4287,11 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4074,12 +4304,22 @@
       </c>
       <c r="AP25" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR25" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS25" t="inlineStr"/>
       <c r="AT25" t="n">
         <v>0</v>
+      </c>
+      <c r="AU25" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV25" t="inlineStr">
         <is>
@@ -4200,6 +4440,11 @@
       <c r="R26" t="n">
         <v>0</v>
       </c>
+      <c r="S26" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4212,12 +4457,22 @@
       </c>
       <c r="AP26" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR26" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS26" t="inlineStr"/>
       <c r="AT26" t="n">
         <v>0</v>
+      </c>
+      <c r="AU26" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV26" t="inlineStr">
         <is>
@@ -4338,6 +4593,11 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
+      <c r="S27" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4350,12 +4610,22 @@
       </c>
       <c r="AP27" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR27" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS27" t="inlineStr"/>
       <c r="AT27" t="n">
         <v>0</v>
+      </c>
+      <c r="AU27" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV27" t="inlineStr">
         <is>
@@ -4476,6 +4746,11 @@
       <c r="R28" t="n">
         <v>0</v>
       </c>
+      <c r="S28" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4488,12 +4763,22 @@
       </c>
       <c r="AP28" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR28" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS28" t="inlineStr"/>
       <c r="AT28" t="n">
         <v>0</v>
+      </c>
+      <c r="AU28" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV28" t="inlineStr">
         <is>
@@ -4614,6 +4899,11 @@
       <c r="R29" t="n">
         <v>0</v>
       </c>
+      <c r="S29" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4626,12 +4916,22 @@
       </c>
       <c r="AP29" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR29" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS29" t="inlineStr"/>
       <c r="AT29" t="n">
         <v>0</v>
+      </c>
+      <c r="AU29" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV29" t="inlineStr">
         <is>
@@ -4752,6 +5052,11 @@
       <c r="R30" t="n">
         <v>0</v>
       </c>
+      <c r="S30" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4764,12 +5069,22 @@
       </c>
       <c r="AP30" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR30" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS30" t="inlineStr"/>
       <c r="AT30" t="n">
         <v>0</v>
+      </c>
+      <c r="AU30" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV30" t="inlineStr">
         <is>
@@ -4890,6 +5205,11 @@
       <c r="R31" t="n">
         <v>0</v>
       </c>
+      <c r="S31" t="inlineStr">
+        <is>
+          <t>wpp_computed</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -4902,12 +5222,22 @@
       </c>
       <c r="AP31" t="inlineStr">
         <is>
-          <t>published_series</t>
+          <t>legacy_fallback</t>
+        </is>
+      </c>
+      <c r="AR31" t="inlineStr">
+        <is>
+          <t>legacy_identity_may_be_lossy</t>
         </is>
       </c>
       <c r="AS31" t="inlineStr"/>
       <c r="AT31" t="n">
         <v>0</v>
+      </c>
+      <c r="AU31" t="inlineStr">
+        <is>
+          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
+        </is>
       </c>
       <c r="AV31" t="inlineStr">
         <is>
